--- a/Result/ModelMetricsResultData.xlsx
+++ b/Result/ModelMetricsResultData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vbshare2\PythonDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99520ED0-13C9-499C-A046-5BB0172B6EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{114F3EF6-DEE8-4B9F-A38D-D8696E5A1565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13890" yWindow="4740" windowWidth="14415" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19965" yWindow="1380" windowWidth="18735" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -85,12 +74,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="182" formatCode="0.000_);[Red]\(0.000\)"/>
-    <numFmt numFmtId="183" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="185" formatCode="0.000_ "/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.000_);[Red]\(0.000\)"/>
+    <numFmt numFmtId="165" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="166" formatCode="0.000_ "/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -101,12 +91,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -180,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -194,32 +186,33 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="183" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="185" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -442,14 +435,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" customWidth="1"/>
-    <col min="3" max="7" width="14.140625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" customWidth="1"/>
+    <col min="3" max="7" width="14.1796875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="18.75" customHeight="1">
       <c r="A1" s="5"/>
       <c r="B1" s="6" t="s">
         <v>13</v>
@@ -470,7 +463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="18.75" customHeight="1">
       <c r="A2" s="16" t="s">
         <v>5</v>
       </c>
@@ -493,7 +486,7 @@
         <v>36.49</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="18.75" customHeight="1">
       <c r="A3" s="17"/>
       <c r="B3" s="2" t="s">
         <v>7</v>
@@ -514,7 +507,7 @@
         <v>37.83</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="18.75" customHeight="1">
       <c r="A4" s="17"/>
       <c r="B4" s="2" t="s">
         <v>8</v>
@@ -535,7 +528,7 @@
         <v>0.25009999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="18.75" customHeight="1">
       <c r="A5" s="17"/>
       <c r="B5" s="2" t="s">
         <v>9</v>
@@ -556,7 +549,7 @@
         <v>-5.9855</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="18.75" customHeight="1">
       <c r="A6" s="16" t="s">
         <v>10</v>
       </c>
@@ -579,7 +572,7 @@
         <v>11.1426</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="18.75" customHeight="1">
       <c r="A7" s="17"/>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -600,7 +593,7 @@
         <v>11.247400000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="18.75" customHeight="1">
       <c r="A8" s="17"/>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -621,7 +614,7 @@
         <v>0.12559999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="18.75" customHeight="1">
       <c r="A9" s="17"/>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -632,17 +625,17 @@
       <c r="D9" s="8">
         <v>0.373</v>
       </c>
-      <c r="E9" s="8">
-        <v>0.45600000000000002</v>
-      </c>
-      <c r="F9" s="8">
-        <v>0.33100000000000002</v>
-      </c>
-      <c r="G9" s="8">
-        <v>7.5999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E9" s="18">
+        <v>-1.8859999999999999</v>
+      </c>
+      <c r="F9" s="18">
+        <v>-0.32190000000000002</v>
+      </c>
+      <c r="G9" s="18">
+        <v>-1.2091000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="18.75" customHeight="1">
       <c r="A10" s="16" t="s">
         <v>11</v>
       </c>
@@ -665,7 +658,7 @@
         <v>6.7565</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="18.75" customHeight="1">
       <c r="A11" s="17"/>
       <c r="B11" s="2" t="s">
         <v>7</v>
@@ -686,7 +679,7 @@
         <v>8.2066999999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="18.75" customHeight="1">
       <c r="A12" s="17"/>
       <c r="B12" s="2" t="s">
         <v>8</v>
@@ -707,7 +700,7 @@
         <v>4.5449999999999997E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="18.75" customHeight="1">
       <c r="A13" s="17"/>
       <c r="B13" s="2" t="s">
         <v>9</v>
@@ -728,7 +721,7 @@
         <v>0.66610000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="18.75" customHeight="1">
       <c r="A14" s="16" t="s">
         <v>12</v>
       </c>
@@ -751,7 +744,7 @@
         <v>11.82072</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="18.75" customHeight="1">
       <c r="A15" s="17"/>
       <c r="B15" s="2" t="s">
         <v>7</v>
@@ -772,7 +765,7 @@
         <v>13.884600000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="18.75" customHeight="1">
       <c r="A16" s="17"/>
       <c r="B16" s="2" t="s">
         <v>8</v>
@@ -798,7 +791,7 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="18.75" customHeight="1">
       <c r="A17" s="17"/>
       <c r="B17" s="2" t="s">
         <v>9</v>
